--- a/examples/demo_template.xlsx
+++ b/examples/demo_template.xlsx
@@ -39,7 +39,7 @@
     <t>头程运费</t>
   </si>
   <si>
-    <t>含税成本</t>
+    <t>包装成本</t>
   </si>
   <si>
     <t>佣金率</t>
@@ -69,7 +69,7 @@
     <t>建议售价</t>
   </si>
   <si>
-    <t>月供测算</t>
+    <t>毛利投产比</t>
   </si>
   <si>
     <t>是否达标</t>
@@ -556,7 +556,7 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>42.5</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -566,8 +566,8 @@
         <v>25.0</v>
       </c>
       <c r="H2" s="2">
-        <f>ROUND(E2*1.13,2)</f>
-        <v>48.03</v>
+        <f>ROUND(E2*0.12,2)</f>
+        <v>4.32</v>
       </c>
       <c r="I2" s="3">
         <f>VLOOKUP(D2,平台费率!$A:$B,2,0)</f>
@@ -577,8 +577,8 @@
         <v>8</v>
       </c>
       <c r="K2" s="2">
-        <f>ROUND((H2+G2+F2*0.05)/F2,2)</f>
-        <v>0.78</v>
+        <f>ROUND(H2+G2+E2*0.05,2)</f>
+        <v>31.12</v>
       </c>
       <c r="L2">
         <v>99</v>
@@ -589,11 +589,11 @@
       </c>
       <c r="N2" s="2">
         <f>ROUND(L2-M2-K2-J2,2)</f>
-        <v>82.3</v>
+        <v>51.96</v>
       </c>
       <c r="O2" s="4">
         <f>ROUND(N2/L2,4)</f>
-        <v>0.8313</v>
+        <v>0.5248</v>
       </c>
       <c r="P2" t="str">
         <f>IF(N2&gt;=30,"A",IF(N2&gt;=20,"B",IF(N2&gt;=10,"C","D")))</f>
@@ -604,8 +604,8 @@
         <v>120</v>
       </c>
       <c r="R2" s="2">
-        <f>ROUND(PMT(0.06/12,12,-L2),2)</f>
-        <v>8.52</v>
+        <f>ROUND(N2/J2,2)</f>
+        <v>6.5</v>
       </c>
       <c r="S2" t="str">
         <f>IF(O2&gt;=0.3,"是","否")</f>
